--- a/Questions - Round 8.xlsx
+++ b/Questions - Round 8.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="67" documentId="11_2EB633F46D2D30F4403DA8967696B337FDF17E34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8533F3C-6006-44D6-8EA1-44BF480B645F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,23 @@
     <sheet name="IT" sheetId="6" r:id="rId6"/>
     <sheet name="PL" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -958,6 +974,183 @@
     <t>Las opciones de movilidad con menos emisiones de carbono reducen las emisiones. Los hábitos personales importan porque muchas pequeñas decisiones cobran importancia cuando muchas personas las repiten.</t>
   </si>
   <si>
+    <t>Qual è l'idea principale dell'OSS 13 – Lotta contro il cambiamento climatico?</t>
+  </si>
+  <si>
+    <t>Facile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
+  </si>
+  <si>
+    <t>Si applica solo ai governi nazionali.</t>
+  </si>
+  <si>
+    <t>È soltanto uno slogan di marketing senza significato pratico.</t>
+  </si>
+  <si>
+    <t>Si concentra sulla mitigazione dei cambiamenti climatici e sull'adattamento ai loro effetti.</t>
+  </si>
+  <si>
+    <t>L'OSS 13 riguarda la mitigazione dei cambiamenti climatici, l'adattamento ai loro effetti e la trasformazione di questo obiettivo in azioni concrete. Diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Perché l'OSS 13 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Scelta singola</t>
+  </si>
+  <si>
+    <t>Perché emissioni, logistica, energia e resilienza possono influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità riguarda solo le relazioni annuali.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Emissioni, logistica, energia e resilienza sono ambiti concreti in cui un'azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle decisioni operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione rappresenta un malinteso comune sull'OSS 13?</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>L'azione per il clima consiste soltanto nel piantare alberi.</t>
+  </si>
+  <si>
+    <t>L'OSS 13 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe eccessivamente l'OSS e nasconde opportunità concrete. Una buona domanda di quiz spesso mette in discussione un'idea errata, perché rende l'apprendimento più memorabile.</t>
+  </si>
+  <si>
+    <t>Quale comportamento traduce meglio l'OSS 13 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento concreto dei comportamenti.</t>
+  </si>
+  <si>
+    <t>Che cosa rende l'OSS 13 un argomento formativo utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Fornisce una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Non è collegato alla cultura aziendale.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>L'apprendimento più efficace avviene quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli OSS sono più coinvolgenti quando risultano pertinenti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Quale quadro contabile viene utilizzato per la contabilizzazione della CO₂ di STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Un sondaggio sulla soddisfazione dei clienti</t>
+  </si>
+  <si>
+    <t>Un foglio di calcolo casuale senza un quadro di riferimento</t>
+  </si>
+  <si>
+    <t>Solo una lista di controllo delle ricevute di carburante</t>
+  </si>
+  <si>
+    <t>La relazione afferma che la contabilizzazione della CO₂ è stata completata in conformità al Greenhouse Gas Protocol. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Qual è l'anno obiettivo dichiarato da STOCKMEIER per raggiungere zero emissioni di carbonio?</t>
+  </si>
+  <si>
+    <t>Difficile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Mai</t>
+  </si>
+  <si>
+    <t>La relazione dichiara l'ambizione di raggiungere zero emissioni di carbonio entro il 2035. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quali attività sostengono l'azione per il clima di STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Ignorare le emissioni della flotta</t>
+  </si>
+  <si>
+    <t>Interrompere i progetti di energia rinnovabile</t>
+  </si>
+  <si>
+    <t>Impianti fotovoltaici ed espansione della mobilità elettrica</t>
+  </si>
+  <si>
+    <t>Ridurre tutte le misurazioni</t>
+  </si>
+  <si>
+    <t>La relazione collega il fotovoltaico, i punti di ricarica, i veicoli elettrici e una fase di test con un camion elettrico alla decarbonizzazione. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>A casa, quale azione riduce solitamente l'impatto sul clima?</t>
+  </si>
+  <si>
+    <t>Riscaldare con le finestre aperte</t>
+  </si>
+  <si>
+    <t>Ignorare completamente l'isolamento</t>
+  </si>
+  <si>
+    <t>Lasciare inutilmente accesi i dispositivi</t>
+  </si>
+  <si>
+    <t>Ridurre il consumo energetico e scegliere apparecchi efficienti</t>
+  </si>
+  <si>
+    <t>Un minore consumo energetico riduce le emissioni associate. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale scelta di trasporto può sostenere l'azione per il clima?</t>
+  </si>
+  <si>
+    <t>Camminare, andare in bicicletta, usare i trasporti pubblici o condividere l'auto quando è pratico</t>
+  </si>
+  <si>
+    <t>Scegliere percorsi più lunghi senza motivo</t>
+  </si>
+  <si>
+    <t>Lasciare inutilmente accesi i motori</t>
+  </si>
+  <si>
+    <t>Guidare da soli per ogni breve tragitto</t>
+  </si>
+  <si>
+    <t>Le scelte di mobilità a basse emissioni di carbonio riducono le emissioni. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
     <t>Jaka jest główna idea Celu Zrównoważonego Rozwoju 13 – Działania w dziedzinie klimatu?</t>
   </si>
   <si>
@@ -1133,190 +1326,13 @@
   </si>
   <si>
     <t>Wybory transportowe o niższej emisji dwutlenku węgla ograniczają emisje. Osobiste nawyki mają znaczenie, ponieważ wiele małych wyborów staje się istotnych, gdy powtarza je wiele osób.</t>
-  </si>
-  <si>
-    <t>Qual è l'idea principale dell'OSS 13 – Lotta contro il cambiamento climatico?</t>
-  </si>
-  <si>
-    <t>Facile · Scelta singola</t>
-  </si>
-  <si>
-    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
-  </si>
-  <si>
-    <t>Si applica solo ai governi nazionali.</t>
-  </si>
-  <si>
-    <t>È soltanto uno slogan di marketing senza significato pratico.</t>
-  </si>
-  <si>
-    <t>Si concentra sulla mitigazione dei cambiamenti climatici e sull'adattamento ai loro effetti.</t>
-  </si>
-  <si>
-    <t>L'OSS 13 riguarda la mitigazione dei cambiamenti climatici, l'adattamento ai loro effetti e la trasformazione di questo obiettivo in azioni concrete. Diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
-  </si>
-  <si>
-    <t>Perché l'OSS 13 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
-  </si>
-  <si>
-    <t>Medio · Scelta singola</t>
-  </si>
-  <si>
-    <t>Perché emissioni, logistica, energia e resilienza possono influire sulle prestazioni di sostenibilità.</t>
-  </si>
-  <si>
-    <t>Perché la sostenibilità riguarda solo le relazioni annuali.</t>
-  </si>
-  <si>
-    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
-  </si>
-  <si>
-    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
-  </si>
-  <si>
-    <t>Emissioni, logistica, energia e resilienza sono ambiti concreti in cui un'azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle decisioni operative quotidiane.</t>
-  </si>
-  <si>
-    <t>Quale affermazione rappresenta un malinteso comune sull'OSS 13?</t>
-  </si>
-  <si>
-    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
-  </si>
-  <si>
-    <t>L'azione per il clima consiste soltanto nel piantare alberi.</t>
-  </si>
-  <si>
-    <t>L'OSS 13 può essere collegato alle decisioni quotidiane.</t>
-  </si>
-  <si>
-    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
-  </si>
-  <si>
-    <t>Questo è il malinteso: restringe eccessivamente l'OSS e nasconde opportunità concrete. Una buona domanda di quiz spesso mette in discussione un'idea errata, perché rende l'apprendimento più memorabile.</t>
-  </si>
-  <si>
-    <t>Quale comportamento traduce meglio l'OSS 13 dalla teoria all'azione?</t>
-  </si>
-  <si>
-    <t>Parlare di sostenibilità senza cambiare nulla.</t>
-  </si>
-  <si>
-    <t>Fare il contrario quando nessuno controlla.</t>
-  </si>
-  <si>
-    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
-  </si>
-  <si>
-    <t>Aspettare che qualcun altro risolva tutto.</t>
-  </si>
-  <si>
-    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento concreto dei comportamenti.</t>
-  </si>
-  <si>
-    <t>Che cosa rende l'OSS 13 un argomento formativo utile per i dipendenti?</t>
-  </si>
-  <si>
-    <t>Fornisce una risposta perfetta per ogni situazione.</t>
-  </si>
-  <si>
-    <t>Non è collegato alla cultura aziendale.</t>
-  </si>
-  <si>
-    <t>Elimina la necessità di conoscenze specialistiche.</t>
-  </si>
-  <si>
-    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
-  </si>
-  <si>
-    <t>L'apprendimento più efficace avviene quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli OSS sono più coinvolgenti quando risultano pertinenti, concreti e collegati ai ruoli delle persone.</t>
-  </si>
-  <si>
-    <t>Quale quadro contabile viene utilizzato per la contabilizzazione della CO₂ di STOCKMEIER?</t>
-  </si>
-  <si>
-    <t>Un sondaggio sulla soddisfazione dei clienti</t>
-  </si>
-  <si>
-    <t>Un foglio di calcolo casuale senza un quadro di riferimento</t>
-  </si>
-  <si>
-    <t>Solo una lista di controllo delle ricevute di carburante</t>
-  </si>
-  <si>
-    <t>La relazione afferma che la contabilizzazione della CO₂ è stata completata in conformità al Greenhouse Gas Protocol. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>Qual è l'anno obiettivo dichiarato da STOCKMEIER per raggiungere zero emissioni di carbonio?</t>
-  </si>
-  <si>
-    <t>Difficile · Scelta singola</t>
-  </si>
-  <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>La relazione dichiara l'ambizione di raggiungere zero emissioni di carbonio entro il 2035. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>Quali attività sostengono l'azione per il clima di STOCKMEIER?</t>
-  </si>
-  <si>
-    <t>Ignorare le emissioni della flotta</t>
-  </si>
-  <si>
-    <t>Interrompere i progetti di energia rinnovabile</t>
-  </si>
-  <si>
-    <t>Impianti fotovoltaici ed espansione della mobilità elettrica</t>
-  </si>
-  <si>
-    <t>Ridurre tutte le misurazioni</t>
-  </si>
-  <si>
-    <t>La relazione collega il fotovoltaico, i punti di ricarica, i veicoli elettrici e una fase di test con un camion elettrico alla decarbonizzazione. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>A casa, quale azione riduce solitamente l'impatto sul clima?</t>
-  </si>
-  <si>
-    <t>Riscaldare con le finestre aperte</t>
-  </si>
-  <si>
-    <t>Ignorare completamente l'isolamento</t>
-  </si>
-  <si>
-    <t>Lasciare inutilmente accesi i dispositivi</t>
-  </si>
-  <si>
-    <t>Ridurre il consumo energetico e scegliere apparecchi efficienti</t>
-  </si>
-  <si>
-    <t>Un minore consumo energetico riduce le emissioni associate. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
-  </si>
-  <si>
-    <t>Quale scelta di trasporto può sostenere l'azione per il clima?</t>
-  </si>
-  <si>
-    <t>Camminare, andare in bicicletta, usare i trasporti pubblici o condividere l'auto quando è pratico</t>
-  </si>
-  <si>
-    <t>Scegliere percorsi più lunghi senza motivo</t>
-  </si>
-  <si>
-    <t>Lasciare inutilmente accesi i motori</t>
-  </si>
-  <si>
-    <t>Guidare da soli per ogni breve tragitto</t>
-  </si>
-  <si>
-    <t>Le scelte di mobilità a basse emissioni di carbonio riducono le emissioni. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1390,7 +1406,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="78">
     <dxf>
@@ -1638,10 +1654,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1664,114 +1676,114 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{55DB4F9F-6A78-4546-8375-56A12CB8F64B}" name="Questions3" displayName="Questions3" ref="A1:J11" headerRowDxfId="67" dataDxfId="65" totalsRowDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{55DB4F9F-6A78-4546-8375-56A12CB8F64B}" name="Questions3" displayName="Questions3" ref="A1:J11" headerRowDxfId="77" dataDxfId="76" totalsRowDxfId="75">
   <autoFilter ref="A1:J11" xr:uid="{55DB4F9F-6A78-4546-8375-56A12CB8F64B}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{84F9B268-07D2-43E9-8766-CD485408CBFB}" name="type" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{B693B98D-2359-40A7-936C-53ED88B54EA9}" name="question" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{D68A69FB-17B0-499D-8EE1-A0CE615C7FAB}" name="note" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{FE2AA486-9B32-4941-B304-218AAF9251DE}" name="option1" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{3F6BE8C0-D7FA-4825-B080-B4E6C9BC7B7E}" name="option2" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{CCF0B658-3C16-4C4D-B895-3B34A27FFEB8}" name="option3" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{4623E796-C23C-4CA3-A25D-5E77837ECB31}" name="option4" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{9E643C12-E44B-4FA4-81DC-6C9128E1D771}" name="correct" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{C9D474E9-9BD5-46D7-8ACE-F653804651BF}" name="explanation" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{22921F8A-ACFB-445D-8A70-9050B0430815}" name="Comments ZF" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{84F9B268-07D2-43E9-8766-CD485408CBFB}" name="type" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{B693B98D-2359-40A7-936C-53ED88B54EA9}" name="question" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{D68A69FB-17B0-499D-8EE1-A0CE615C7FAB}" name="note" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{FE2AA486-9B32-4941-B304-218AAF9251DE}" name="option1" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{3F6BE8C0-D7FA-4825-B080-B4E6C9BC7B7E}" name="option2" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{CCF0B658-3C16-4C4D-B895-3B34A27FFEB8}" name="option3" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{4623E796-C23C-4CA3-A25D-5E77837ECB31}" name="option4" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{9E643C12-E44B-4FA4-81DC-6C9128E1D771}" name="correct" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{C9D474E9-9BD5-46D7-8ACE-F653804651BF}" name="explanation" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{22921F8A-ACFB-445D-8A70-9050B0430815}" name="Comments ZF" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BBF7B9-BD8F-4F84-A53E-5E8AA640A534}" name="Questions4" displayName="Questions4" ref="A1:J11" headerRowDxfId="54" dataDxfId="52" totalsRowDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BBF7B9-BD8F-4F84-A53E-5E8AA640A534}" name="Questions4" displayName="Questions4" ref="A1:J11" headerRowDxfId="64" dataDxfId="63" totalsRowDxfId="62">
   <autoFilter ref="A1:J11" xr:uid="{21BBF7B9-BD8F-4F84-A53E-5E8AA640A534}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{ACF2C0CA-59C5-4637-A370-819155DD6A4D}" name="type" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{1EA93686-D75C-48F5-BFBF-90668A8AC7B9}" name="question" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{7EE99973-C25E-4C33-8424-F941D3D9CC29}" name="note" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{79D3BE1C-73F7-4FD1-966E-3D45270E3632}" name="option1" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{49A639FF-54DF-4734-B045-4296F7FD58CC}" name="option2" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{8E924DAB-1186-4200-B74D-5686DC8C7B49}" name="option3" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{832708A3-16A0-4EF2-80CB-DE4BF8C2306D}" name="option4" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{1A9261C7-47FE-4125-8CF0-659F125800D1}" name="correct" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{088A2BCD-F4AC-42F1-A919-89365295BF6C}" name="explanation" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{55953ADC-7C55-4F7C-8E20-3B43F78A90A8}" name="Comments ZF" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{ACF2C0CA-59C5-4637-A370-819155DD6A4D}" name="type" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{1EA93686-D75C-48F5-BFBF-90668A8AC7B9}" name="question" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{7EE99973-C25E-4C33-8424-F941D3D9CC29}" name="note" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{79D3BE1C-73F7-4FD1-966E-3D45270E3632}" name="option1" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{49A639FF-54DF-4734-B045-4296F7FD58CC}" name="option2" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{8E924DAB-1186-4200-B74D-5686DC8C7B49}" name="option3" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{832708A3-16A0-4EF2-80CB-DE4BF8C2306D}" name="option4" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{1A9261C7-47FE-4125-8CF0-659F125800D1}" name="correct" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{088A2BCD-F4AC-42F1-A919-89365295BF6C}" name="explanation" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{55953ADC-7C55-4F7C-8E20-3B43F78A90A8}" name="Comments ZF" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{01DFE7A8-0821-4B9B-8F19-D6DED8FE8028}" name="Questions5" displayName="Questions5" ref="A1:J11" headerRowDxfId="41" dataDxfId="39" totalsRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{01DFE7A8-0821-4B9B-8F19-D6DED8FE8028}" name="Questions5" displayName="Questions5" ref="A1:J11" headerRowDxfId="51" dataDxfId="50" totalsRowDxfId="49">
   <autoFilter ref="A1:J11" xr:uid="{01DFE7A8-0821-4B9B-8F19-D6DED8FE8028}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3779A36D-0E0C-4BC6-BAB5-C3EE2D154AFD}" name="type" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{FA2968F5-01A8-4E63-8F3A-00B0448FE1C9}" name="question" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{4F0162A3-7945-4B76-BE4E-AEA45BCC5B2C}" name="note" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{66ADC4B0-C1DE-446A-8ECE-AFA9CE6D6782}" name="option1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{DE36129E-D399-4DAC-8853-985FA3FF255F}" name="option2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{E7AC7C53-2A16-480B-8766-FDA1040948A7}" name="option3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{21FD10A8-BAAC-4A5B-A962-0406BEBFD5AF}" name="option4" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{D6365EF8-D5A6-4E1B-9E46-F23FAEC2AC94}" name="correct" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{19247EDB-5308-4D4C-B5DA-3B4E3A5C250D}" name="explanation" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{845746BD-C88B-4853-9CA3-38C477948933}" name="Comments ZF" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{3779A36D-0E0C-4BC6-BAB5-C3EE2D154AFD}" name="type" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{FA2968F5-01A8-4E63-8F3A-00B0448FE1C9}" name="question" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{4F0162A3-7945-4B76-BE4E-AEA45BCC5B2C}" name="note" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{66ADC4B0-C1DE-446A-8ECE-AFA9CE6D6782}" name="option1" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{DE36129E-D399-4DAC-8853-985FA3FF255F}" name="option2" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{E7AC7C53-2A16-480B-8766-FDA1040948A7}" name="option3" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{21FD10A8-BAAC-4A5B-A962-0406BEBFD5AF}" name="option4" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{D6365EF8-D5A6-4E1B-9E46-F23FAEC2AC94}" name="correct" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{19247EDB-5308-4D4C-B5DA-3B4E3A5C250D}" name="explanation" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{845746BD-C88B-4853-9CA3-38C477948933}" name="Comments ZF" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{725DF7D6-66D5-414C-803E-E80082C45A40}" name="Questions6" displayName="Questions6" ref="A1:J11" headerRowDxfId="28" dataDxfId="26" totalsRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{725DF7D6-66D5-414C-803E-E80082C45A40}" name="Questions6" displayName="Questions6" ref="A1:J11" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="36">
   <autoFilter ref="A1:J11" xr:uid="{725DF7D6-66D5-414C-803E-E80082C45A40}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6BE4C8F0-E1F6-484B-B0EC-04FF28AB1C40}" name="type" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{232FE9DC-3BB3-4EA6-A7D0-106919A6D7E8}" name="question" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{672E0127-1490-44E5-8C7F-0B21FE94A0E2}" name="note" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{3ECB44D7-67AA-487F-8ABD-6A6BDEB0AF9E}" name="option1" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{3AC69C89-090E-4878-B6A8-FD6AE51A5095}" name="option2" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{AA76EFE7-DF2D-41FE-B1F5-FE5F3614C6C1}" name="option3" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{42E376EB-BCEC-4049-936C-F6B7C144385F}" name="option4" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{2D6EF48A-F973-48D9-8CFD-9E3B75D10D03}" name="correct" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{0FD4B576-AB22-47EB-B518-FB596FC53D8B}" name="explanation" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{9D2A3090-313F-431C-B0E8-2CDDE57BDFBE}" name="Comments ZF" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{6BE4C8F0-E1F6-484B-B0EC-04FF28AB1C40}" name="type" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{232FE9DC-3BB3-4EA6-A7D0-106919A6D7E8}" name="question" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{672E0127-1490-44E5-8C7F-0B21FE94A0E2}" name="note" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{3ECB44D7-67AA-487F-8ABD-6A6BDEB0AF9E}" name="option1" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{3AC69C89-090E-4878-B6A8-FD6AE51A5095}" name="option2" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{AA76EFE7-DF2D-41FE-B1F5-FE5F3614C6C1}" name="option3" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{42E376EB-BCEC-4049-936C-F6B7C144385F}" name="option4" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{2D6EF48A-F973-48D9-8CFD-9E3B75D10D03}" name="correct" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{0FD4B576-AB22-47EB-B518-FB596FC53D8B}" name="explanation" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{9D2A3090-313F-431C-B0E8-2CDDE57BDFBE}" name="Comments ZF" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{946CB7AE-F174-490F-B68D-6D532571FE43}" name="Questions8" displayName="Questions8" ref="A1:J11" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{946CB7AE-F174-490F-B68D-6D532571FE43}" name="Questions8" displayName="Questions8" ref="A1:J11" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
   <autoFilter ref="A1:J11" xr:uid="{946CB7AE-F174-490F-B68D-6D532571FE43}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7A1B5559-3764-456B-98FB-5110E54718EC}" name="type" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{351AA846-AF55-4434-9C81-E58E29ACF692}" name="question" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{1EA230B8-9D6C-42BD-AE91-109A1852123E}" name="note" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{729EB6E3-ACE0-4B1E-B1E4-A57C895C5D82}" name="option1" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{872FB033-6A0D-487E-B638-241ABE5E018E}" name="option2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{0B3507AC-A8FD-4F02-AEF7-56A26FAA409E}" name="option3" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{71C5BDE2-F656-4A95-989E-7F3B0FF13E11}" name="option4" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{09369FD7-14DB-43CA-B3E8-CC92FCB78451}" name="correct" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{6D80B85B-9C36-425B-A670-BB7809B93E29}" name="explanation" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{EF5C1464-F567-4485-AD1A-59A10A15F545}" name="Comments ZF" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{7A1B5559-3764-456B-98FB-5110E54718EC}" name="type" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{351AA846-AF55-4434-9C81-E58E29ACF692}" name="question" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{1EA230B8-9D6C-42BD-AE91-109A1852123E}" name="note" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{729EB6E3-ACE0-4B1E-B1E4-A57C895C5D82}" name="option1" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{872FB033-6A0D-487E-B638-241ABE5E018E}" name="option2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{0B3507AC-A8FD-4F02-AEF7-56A26FAA409E}" name="option3" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{71C5BDE2-F656-4A95-989E-7F3B0FF13E11}" name="option4" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{09369FD7-14DB-43CA-B3E8-CC92FCB78451}" name="correct" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{6D80B85B-9C36-425B-A670-BB7809B93E29}" name="explanation" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{EF5C1464-F567-4485-AD1A-59A10A15F545}" name="Comments ZF" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6A7ED759-7F23-41DE-9F22-81EDA0F0F182}" name="Questions7" displayName="Questions7" ref="A1:J11" headerRowDxfId="15" dataDxfId="13" totalsRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6A7ED759-7F23-41DE-9F22-81EDA0F0F182}" name="Questions7" displayName="Questions7" ref="A1:J11" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="10">
   <autoFilter ref="A1:J11" xr:uid="{6A7ED759-7F23-41DE-9F22-81EDA0F0F182}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{EC6FB354-B591-4AE7-A591-5301E75C7728}" name="type" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{377E70D5-C0D0-473A-A7A6-D7144F25B6C2}" name="question" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{06C02334-9AB8-429D-A14D-24C77494D7D6}" name="note" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{251728DE-525F-4CEB-9DF9-0B1CF6B71360}" name="option1" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{2BF270FD-6C56-4954-9011-983172048827}" name="option2" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{C3A6C8B9-86A4-4EED-841E-BDB12B2CA084}" name="option3" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{D2292937-77F2-4C6C-B758-5A485FB37DD1}" name="option4" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{780A1EA1-BC42-445B-9EB3-27DA7138A0E7}" name="correct" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{BB4D7647-C5BD-41DD-B015-FC21C4454D0C}" name="explanation" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{7B3A2943-E789-4725-AF57-8E193DD044C1}" name="Comments ZF" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{EC6FB354-B591-4AE7-A591-5301E75C7728}" name="type" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{377E70D5-C0D0-473A-A7A6-D7144F25B6C2}" name="question" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{06C02334-9AB8-429D-A14D-24C77494D7D6}" name="note" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{251728DE-525F-4CEB-9DF9-0B1CF6B71360}" name="option1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{2BF270FD-6C56-4954-9011-983172048827}" name="option2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{C3A6C8B9-86A4-4EED-841E-BDB12B2CA084}" name="option3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{D2292937-77F2-4C6C-B758-5A485FB37DD1}" name="option4" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{780A1EA1-BC42-445B-9EB3-27DA7138A0E7}" name="correct" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{BB4D7647-C5BD-41DD-B015-FC21C4454D0C}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{7B3A2943-E789-4725-AF57-8E193DD044C1}" name="Comments ZF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2063,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2074,7 +2086,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2106,7 +2118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="72" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2136,7 +2148,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2166,7 +2178,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2196,7 +2208,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2226,7 +2238,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2256,7 +2268,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2286,7 +2298,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2316,7 +2328,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2346,7 +2358,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2376,7 +2388,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2417,18 +2429,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA8A443-24F1-45FD-A962-E0BE7CF1CD47}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2460,7 +2472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.95">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2490,7 +2502,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2520,7 +2532,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="43.5">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2550,7 +2562,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2580,7 +2592,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.95">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2640,7 +2652,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="43.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2670,7 +2682,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="57.95">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2700,7 +2712,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2730,7 +2742,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="43.5">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2771,18 +2783,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD6E7C5-B556-4670-8314-8A0E3287CA1D}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2814,7 +2826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.95">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2844,7 +2856,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="57.95">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2874,7 +2886,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="57.95">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2904,7 +2916,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2934,7 +2946,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2964,7 +2976,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.95">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2994,7 +3006,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="57.95">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3024,7 +3036,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72.599999999999994">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3054,7 +3066,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="57.95">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3084,7 +3096,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.95">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3125,18 +3137,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BCA1D2-37B1-427D-BCAC-976E6220B12A}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.95">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3198,7 +3210,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3228,7 +3240,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="43.5">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3258,7 +3270,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3288,7 +3300,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3318,7 +3330,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.95">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3348,7 +3360,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="43.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3378,7 +3390,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72.599999999999994">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3408,7 +3420,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="57.95">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3438,7 +3450,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.95">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3479,18 +3491,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791627C6-4BCD-4C46-8206-F85D4227A429}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3522,7 +3534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.95">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3552,7 +3564,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="57.95">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3582,7 +3594,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="57.95">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3612,7 +3624,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3642,7 +3654,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3684,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.95">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3702,7 +3714,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="57.95">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3732,7 +3744,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72.599999999999994">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3762,7 +3774,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3792,7 +3804,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.95">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3833,18 +3845,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0797CF35-5733-460B-9E0D-88C65CADC66B}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3876,195 +3888,195 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="57.95">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>369</v>
+        <v>310</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>371</v>
+        <v>312</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>372</v>
+        <v>313</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="H2" s="2">
         <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>375</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>376</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>380</v>
+        <v>321</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="57.95">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>387</v>
+        <v>328</v>
       </c>
       <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>391</v>
+        <v>332</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>398</v>
+        <v>339</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>399</v>
+        <v>340</v>
       </c>
       <c r="H6" s="2">
         <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="57.95">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>401</v>
+        <v>342</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>402</v>
+        <v>343</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>403</v>
+        <v>344</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>404</v>
+        <v>345</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="57.95">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>406</v>
+        <v>347</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D8" s="4">
         <v>2028</v>
@@ -4076,103 +4088,103 @@
         <v>2050</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>408</v>
+        <v>349</v>
       </c>
       <c r="H8" s="2">
         <v>2</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="57.95">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>410</v>
+        <v>351</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>412</v>
+        <v>353</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>414</v>
+        <v>355</v>
       </c>
       <c r="H9" s="2">
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>418</v>
+        <v>359</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>420</v>
+        <v>361</v>
       </c>
       <c r="H10" s="2">
         <v>4</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.95">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>422</v>
+        <v>363</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>423</v>
+        <v>364</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>425</v>
+        <v>366</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="J11" s="2"/>
     </row>
@@ -4187,18 +4199,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE4D5AB-2894-49F8-814B-DE7C4BA2F2E5}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="58.1796875" customWidth="1"/>
-    <col min="10" max="10" width="16.36328125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4230,195 +4242,195 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.5">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="H2" s="2">
         <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="57.95">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="57.95">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="H6" s="2">
         <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="43.5">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>346</v>
+        <v>405</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="43.5">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="D8" s="4">
         <v>2028</v>
@@ -4430,103 +4442,103 @@
         <v>2050</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="H8" s="2">
         <v>2</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="57.95">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="H9" s="2">
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="H10" s="2">
         <v>4</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>362</v>
+        <v>421</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="43.5">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="J11" s="2"/>
     </row>
@@ -4539,12 +4551,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4712,47 +4725,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A41E475F-09D6-4954-8437-0C41072760B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6112DC0B-2A78-45CA-939E-7C4A768D713B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29395FB7-320F-4FF3-B4B0-1274905D49B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF5B5D21-B061-422A-9BBA-E77F4F99ADB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6112DC0B-2A78-45CA-939E-7C4A768D713B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A41E475F-09D6-4954-8437-0C41072760B4}"/>
 </file>